--- a/Mantenimiento/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
+++ b/Mantenimiento/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1420,11 +1330,6 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1472,11 +1377,6 @@
       <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1523,11 +1423,6 @@
       </c>
       <c r="K21" t="n">
         <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
+++ b/Mantenimiento/excels/AREQUIPA-CAYLLOMA-MAJES.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>SAGRADA FAMILIA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-16.36175</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-72.19129</v>
-      </c>
-      <c r="I2" t="n">
-        <v>345</v>
-      </c>
-      <c r="J2" t="n">
-        <v>19</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-16.36175</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-72.19129</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>40201 TECNICO AGROPECUARIO LA COLINA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-16.3442</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-72.177381</v>
-      </c>
-      <c r="I3" t="n">
-        <v>399</v>
-      </c>
-      <c r="J3" t="n">
-        <v>23</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-16.3442</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-72.177381</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>40230 SAN ANTONIO DEL PEDREGAL</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-16.355583</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-72.188064</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1561</v>
-      </c>
-      <c r="J4" t="n">
-        <v>66</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-16.355583</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-72.188064</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>40625 CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-16.319544</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-72.239278</v>
-      </c>
-      <c r="I5" t="n">
-        <v>740</v>
-      </c>
-      <c r="J5" t="n">
-        <v>41</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-16.319544</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-72.239278</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>40629 DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-16.313314</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-72.281154</v>
-      </c>
-      <c r="I6" t="n">
-        <v>400</v>
-      </c>
-      <c r="J6" t="n">
-        <v>27</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-16.313314</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-72.281154</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>41061 JOSE ANTONIO ENCINAS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-16.350267</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-72.28175400000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>726</v>
-      </c>
-      <c r="J7" t="n">
-        <v>44</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-16.350267</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-72.281754</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-16.358157</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-72.189531</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1352</v>
-      </c>
-      <c r="J8" t="n">
-        <v>63</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-16.358157</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-72.189531</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1352</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>NUESTRA SRA. DE LA PAZ</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-16.328735</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-72.26320200000001</v>
-      </c>
-      <c r="I9" t="n">
-        <v>323</v>
-      </c>
-      <c r="J9" t="n">
-        <v>15</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-16.328735</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-72.263202</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>JUSTO JUEZ</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-16.35287</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-72.18816</v>
-      </c>
-      <c r="I10" t="n">
-        <v>248</v>
-      </c>
-      <c r="J10" t="n">
-        <v>28</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-16.35287</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-72.18816</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>JOSE A. QUIÑONES GONZALES</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-16.3619</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-72.18931000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>168</v>
-      </c>
-      <c r="J11" t="n">
-        <v>12</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-16.3619</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-72.18931</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>40698 SAN JUAN BAUTISTA DE MAJES</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-16.373064</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-72.198442</v>
-      </c>
-      <c r="I12" t="n">
-        <v>210</v>
-      </c>
-      <c r="J12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-16.373064</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-72.198442</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>40201 TECNICO AGROPECUARIO LA COLINA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-16.340892</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-72.17423100000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>365</v>
-      </c>
-      <c r="J13" t="n">
-        <v>15</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-16.340892</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-72.174231</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1080,20 +1188,30 @@
           <t>BELAUNDE TERRY</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-16.342191</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-72.183762</v>
-      </c>
-      <c r="I14" t="n">
-        <v>270</v>
-      </c>
-      <c r="J14" t="n">
-        <v>10</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-16.342191</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-72.183762</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1127,20 +1245,30 @@
           <t>CORONEL FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-16.321544</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-72.18002</v>
-      </c>
-      <c r="I15" t="n">
-        <v>854</v>
-      </c>
-      <c r="J15" t="n">
-        <v>34</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-16.321544</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-72.18002</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1174,20 +1302,30 @@
           <t>LOS DINAMICOS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-16.38503</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-72.20285</v>
-      </c>
-      <c r="I16" t="n">
-        <v>334</v>
-      </c>
-      <c r="J16" t="n">
-        <v>14</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-16.38503</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-72.20285</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1221,20 +1359,30 @@
           <t>DR JUAN MANUEL GUILLEN BENAVIDES</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-16.342904</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-72.189876</v>
-      </c>
-      <c r="I17" t="n">
-        <v>382</v>
-      </c>
-      <c r="J17" t="n">
-        <v>17</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-16.342904</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-72.189876</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1268,20 +1416,30 @@
           <t>CIENCIAS</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-16.35999</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-72.1892</v>
-      </c>
-      <c r="I18" t="n">
-        <v>267</v>
-      </c>
-      <c r="J18" t="n">
-        <v>12</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-16.35999</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-72.1892</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1315,20 +1473,30 @@
           <t>SAN CARLOS</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-16.36045</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-72.19092999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>362</v>
-      </c>
-      <c r="J19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-16.36045</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-72.19093</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1362,20 +1530,30 @@
           <t>BRYCE PEDREGAL</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-16.36371</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-72.19053</v>
-      </c>
-      <c r="I20" t="n">
-        <v>187</v>
-      </c>
-      <c r="J20" t="n">
-        <v>23</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-16.36371</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-72.19053</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1409,20 +1587,30 @@
           <t>MARIA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-16.35426</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-72.18845</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-16.35426</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-72.18845</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
